--- a/data/trans_orig/Q5405-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5405-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2007</t>
+          <t>Población según si es capaz de usar un telefono en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98475</t>
+          <t>98327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110318</t>
+          <t>109581</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136298</t>
+          <t>137329</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147135</t>
+          <t>147466</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>239909</t>
+          <t>239534</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>255337</t>
+          <t>255516</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>16029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>18699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15435</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133633</t>
+          <t>132720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143100</t>
+          <t>143128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158484</t>
+          <t>157098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>173923</t>
+          <t>174228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296360</t>
+          <t>295663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314809</t>
+          <t>314911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93250</t>
+          <t>93774</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102669</t>
+          <t>103349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124608</t>
+          <t>124825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134026</t>
+          <t>134028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>222343</t>
+          <t>222743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>235594</t>
+          <t>235460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13892</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126415</t>
+          <t>125590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134772</t>
+          <t>134719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190832</t>
+          <t>191487</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203729</t>
+          <t>203770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>321064</t>
+          <t>321014</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>336495</t>
+          <t>336283</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29483</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37626</t>
+          <t>39384</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>25852</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48682</t>
+          <t>50437</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>464527</t>
+          <t>465631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>484236</t>
+          <t>484742</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>626513</t>
+          <t>626134</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>650828</t>
+          <t>650983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1099923</t>
+          <t>1099217</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1129310</t>
+          <t>1128971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2012</t>
+          <t>Población según si es capaz de usar un telefono en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>15634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121780</t>
+          <t>120517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134191</t>
+          <t>134289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143983</t>
+          <t>143014</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159105</t>
+          <t>158323</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270364</t>
+          <t>269984</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>290389</t>
+          <t>290226</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16798</t>
+          <t>15855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>23454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22734</t>
+          <t>22086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23558</t>
+          <t>25674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>41724</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123742</t>
+          <t>125813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142568</t>
+          <t>143281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157199</t>
+          <t>157230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175639</t>
+          <t>175912</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287803</t>
+          <t>287563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>315065</t>
+          <t>313433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>12483</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21882</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>18704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28360</t>
+          <t>26922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83580</t>
+          <t>83019</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98152</t>
+          <t>98227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111974</t>
+          <t>113128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129649</t>
+          <t>129955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203302</t>
+          <t>202613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225595</t>
+          <t>225110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -4613,47 +4613,47 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>8223</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>9312</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9312</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21763</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34741</t>
+          <t>34676</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>137018</t>
+          <t>136780</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153586</t>
+          <t>153659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212321</t>
+          <t>212983</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>230319</t>
+          <t>230331</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>357447</t>
+          <t>356131</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>381017</t>
+          <t>380339</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>29849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44565</t>
+          <t>43281</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37623</t>
+          <t>37460</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67248</t>
+          <t>66541</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24857</t>
+          <t>24726</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>51864</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35180</t>
+          <t>34045</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61889</t>
+          <t>60469</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>65160</t>
+          <t>64038</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102921</t>
+          <t>102167</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>485960</t>
+          <t>486521</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>517658</t>
+          <t>517838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>646870</t>
+          <t>647417</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>680195</t>
+          <t>681466</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1143495</t>
+          <t>1146378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1191566</t>
+          <t>1192250</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2016</t>
+          <t>Población según si es capaz de usar un telefono en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17409</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>19333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125104</t>
+          <t>125030</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134290</t>
+          <t>134278</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153274</t>
+          <t>153420</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167692</t>
+          <t>167663</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>283913</t>
+          <t>282952</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>299829</t>
+          <t>299686</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25609</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31335</t>
+          <t>31124</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150215</t>
+          <t>150086</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160581</t>
+          <t>160512</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>190370</t>
+          <t>189744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>209491</t>
+          <t>208868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>345989</t>
+          <t>345711</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366991</t>
+          <t>367508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106392</t>
+          <t>106299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114137</t>
+          <t>114138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116574</t>
+          <t>117129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133845</t>
+          <t>133919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>226765</t>
+          <t>227260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245988</t>
+          <t>245449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22773</t>
+          <t>23104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163536</t>
+          <t>163230</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172324</t>
+          <t>172613</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>220785</t>
+          <t>221275</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>237058</t>
+          <t>236713</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>389729</t>
+          <t>389258</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>407672</t>
+          <t>407038</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28741</t>
+          <t>29236</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56157</t>
+          <t>56384</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>40845</t>
+          <t>41115</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71434</t>
+          <t>71242</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>557744</t>
+          <t>558402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>576118</t>
+          <t>575653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>702505</t>
+          <t>702817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>734755</t>
+          <t>734475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1267298</t>
+          <t>1270269</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1305623</t>
+          <t>1305511</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2023</t>
+          <t>Población según si es capaz de usar un telefono en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>13011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135186</t>
+          <t>134801</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143730</t>
+          <t>143484</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>159973</t>
+          <t>159579</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169129</t>
+          <t>168598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>298201</t>
+          <t>298051</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310193</t>
+          <t>310540</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>14437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>11558</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23671</t>
+          <t>23479</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149924</t>
+          <t>149819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157443</t>
+          <t>157190</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>191548</t>
+          <t>192007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>204019</t>
+          <t>204300</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344379</t>
+          <t>344599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>359361</t>
+          <t>359561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12174</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>12139</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>24753</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129985</t>
+          <t>130057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136141</t>
+          <t>136131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>324765</t>
+          <t>325805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357521</t>
+          <t>356616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>466619</t>
+          <t>466965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>493073</t>
+          <t>492502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14454</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15426</t>
+          <t>15357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195076</t>
+          <t>195695</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202788</t>
+          <t>202628</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>252925</t>
+          <t>252472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>264842</t>
+          <t>264226</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>451724</t>
+          <t>451583</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>465520</t>
+          <t>465443</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33505</t>
+          <t>32824</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>19598</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40177</t>
+          <t>40932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21825</t>
+          <t>21135</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54235</t>
+          <t>53661</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>35883</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68477</t>
+          <t>67752</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>621210</t>
+          <t>620766</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>635018</t>
+          <t>635141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>948870</t>
+          <t>949625</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1000088</t>
+          <t>1002534</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1578633</t>
+          <t>1580236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1628327</t>
+          <t>1625466</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5405-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5405-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>14591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98327</t>
+          <t>99335</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109581</t>
+          <t>110306</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>137329</t>
+          <t>137015</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147466</t>
+          <t>147236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>239534</t>
+          <t>239101</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>255516</t>
+          <t>255048</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16029</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>18365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20632</t>
+          <t>21609</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132720</t>
+          <t>133260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143128</t>
+          <t>143848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157098</t>
+          <t>156544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174228</t>
+          <t>174079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295663</t>
+          <t>294941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314911</t>
+          <t>314793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93774</t>
+          <t>93075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103349</t>
+          <t>102660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124825</t>
+          <t>125441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134028</t>
+          <t>134043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>222743</t>
+          <t>221249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>235460</t>
+          <t>235330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11608</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125590</t>
+          <t>126413</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134719</t>
+          <t>134744</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191487</t>
+          <t>190707</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203770</t>
+          <t>203677</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>321014</t>
+          <t>320962</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>336283</t>
+          <t>336755</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17292</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39384</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28255</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26524</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50437</t>
+          <t>50270</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>465631</t>
+          <t>464648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>484742</t>
+          <t>484327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>626134</t>
+          <t>627579</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>650983</t>
+          <t>650948</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1099217</t>
+          <t>1099327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1128971</t>
+          <t>1130302</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18845</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,47 +3408,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>13717</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>7443</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>21833</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>2,43%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>13717</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>7481</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>22332</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120517</t>
+          <t>121414</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134289</t>
+          <t>134178</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143014</t>
+          <t>144308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158323</t>
+          <t>158589</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>269984</t>
+          <t>270455</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>290226</t>
+          <t>290156</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15855</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23454</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22086</t>
+          <t>23353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9067</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25674</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>41724</t>
+          <t>42231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125813</t>
+          <t>125459</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143281</t>
+          <t>142919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157230</t>
+          <t>156303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175912</t>
+          <t>175101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287563</t>
+          <t>289079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313433</t>
+          <t>315134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15830</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>21135</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18704</t>
+          <t>18518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83019</t>
+          <t>83563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98227</t>
+          <t>97878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113128</t>
+          <t>112552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129955</t>
+          <t>129932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202613</t>
+          <t>203074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225110</t>
+          <t>224280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21098</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>22150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>19220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34676</t>
+          <t>35115</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136780</t>
+          <t>137066</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153659</t>
+          <t>153471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212983</t>
+          <t>213097</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>230331</t>
+          <t>230428</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356131</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>380339</t>
+          <t>381477</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29849</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43281</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37460</t>
+          <t>38376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66541</t>
+          <t>67782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34045</t>
+          <t>33010</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60469</t>
+          <t>61037</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>64038</t>
+          <t>63989</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102167</t>
+          <t>101298</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>486521</t>
+          <t>486612</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>517838</t>
+          <t>517510</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>647417</t>
+          <t>648182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>681466</t>
+          <t>681602</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1146378</t>
+          <t>1146537</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1192250</t>
+          <t>1191621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19333</t>
+          <t>19660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125030</t>
+          <t>125043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134278</t>
+          <t>134221</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153420</t>
+          <t>153370</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167663</t>
+          <t>167635</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>282952</t>
+          <t>282564</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>299686</t>
+          <t>299742</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25204</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31124</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150086</t>
+          <t>148779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160512</t>
+          <t>160608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>189744</t>
+          <t>191622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208868</t>
+          <t>208926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>345711</t>
+          <t>347757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367508</t>
+          <t>368408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16799</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106299</t>
+          <t>106799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114138</t>
+          <t>114148</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117129</t>
+          <t>116806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133919</t>
+          <t>133819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227260</t>
+          <t>226977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245449</t>
+          <t>245788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163230</t>
+          <t>162288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172613</t>
+          <t>172200</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>221275</t>
+          <t>220897</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>236713</t>
+          <t>236477</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>389258</t>
+          <t>390415</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>407038</t>
+          <t>407307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26625</t>
+          <t>25536</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>16789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>38095</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29236</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56384</t>
+          <t>57116</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>42085</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71242</t>
+          <t>72385</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>558402</t>
+          <t>557263</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>575653</t>
+          <t>575894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>702817</t>
+          <t>702674</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>734475</t>
+          <t>735218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1270269</t>
+          <t>1270290</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1305511</t>
+          <t>1305082</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14469</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>140211</t>
+          <t>155382</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134801</t>
+          <t>150638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143484</t>
+          <t>158893</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>164895</t>
+          <t>176195</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>159579</t>
+          <t>170572</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168598</t>
+          <t>180561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>305107</t>
+          <t>331577</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>298051</t>
+          <t>324747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310540</t>
+          <t>337484</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>471</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11558</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23479</t>
+          <t>24789</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>154099</t>
+          <t>172023</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149819</t>
+          <t>167029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157190</t>
+          <t>175203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>198866</t>
+          <t>221149</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192007</t>
+          <t>213117</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>204300</t>
+          <t>226341</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>352965</t>
+          <t>393171</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344599</t>
+          <t>384867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>359561</t>
+          <t>400300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>922</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5406</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24753</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>134376</t>
+          <t>157028</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130057</t>
+          <t>152407</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136131</t>
+          <t>158884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>346671</t>
+          <t>160376</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>325805</t>
+          <t>153375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>356616</t>
+          <t>166206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>481048</t>
+          <t>317404</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>466965</t>
+          <t>308733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>492502</t>
+          <t>322458</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,17 +9667,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>17438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>199978</t>
+          <t>209977</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195695</t>
+          <t>205153</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202628</t>
+          <t>212679</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>259149</t>
+          <t>276810</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>252472</t>
+          <t>268458</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>264226</t>
+          <t>282798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>459127</t>
+          <t>486787</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>451583</t>
+          <t>477113</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>465443</t>
+          <t>493369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>274920</t>
+          <t>294461</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>274920</t>
+          <t>294461</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>274920</t>
+          <t>294461</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>479949</t>
+          <t>509550</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>479949</t>
+          <t>509550</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>479949</t>
+          <t>509550</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>25510</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>33615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>30573</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40932</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21135</t>
+          <t>22873</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39686</t>
+          <t>42399</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20465</t>
+          <t>33943</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53661</t>
+          <t>52749</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>54445</t>
+          <t>57709</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>46680</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>67752</t>
+          <t>69330</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>628664</t>
+          <t>694410</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>620766</t>
+          <t>685616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>635141</t>
+          <t>700632</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>969582</t>
+          <t>834530</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>949625</t>
+          <t>821131</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1002534</t>
+          <t>845724</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1598246</t>
+          <t>1528940</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1580236</t>
+          <t>1514621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1625466</t>
+          <t>1542535</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1033086</t>
+          <t>902439</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033086</t>
+          <t>902439</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1033086</t>
+          <t>902439</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1683264</t>
+          <t>1618830</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1683264</t>
+          <t>1618830</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1683264</t>
+          <t>1618830</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
